--- a/artfynd/A 44645-2025 artfynd.xlsx
+++ b/artfynd/A 44645-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601409</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44645-2025 artfynd.xlsx
+++ b/artfynd/A 44645-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601409</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44645-2025 artfynd.xlsx
+++ b/artfynd/A 44645-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601409</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
